--- a/VerveStacks_NOR_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NOR_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5485870-DEF3-4DFB-A333-850950685501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{716F67B7-4ECB-4DCA-B1D6-A6B10EFD51E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4012" yWindow="4012" windowWidth="21601" windowHeight="11423" xr2:uid="{ABE32361-0D84-4CB1-90B3-F73A3AC831A0}"/>
+    <workbookView xWindow="4012" yWindow="4012" windowWidth="21601" windowHeight="11423" xr2:uid="{1E5F381A-FF7A-431D-846D-CFE6C42EEB9B}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1304,7 +1304,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D91B5CCC-92C5-432C-B94B-A33C112995B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4427B69F-56CD-4516-92C4-86BB06C03431}">
   <dimension ref="B3:S116"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
